--- a/SCIE용/산출물/엑셀/15_g1_g2_g3_g4_summary.xlsx
+++ b/SCIE용/산출물/엑셀/15_g1_g2_g3_g4_summary.xlsx
@@ -163,7 +163,7 @@
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
@@ -173,7 +173,7 @@
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>0.827</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -220,12 +220,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -235,7 +235,7 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -282,12 +282,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -297,37 +297,37 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>0.534</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>84.3%</t>
         </is>
       </c>
     </row>
@@ -339,57 +339,57 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>자동 단계 분류 기반 상황 인지형 멀티모달 RAG</t>
+          <t>단계 추정 기반 상황 인지형 멀티모달 RAG</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84.3%</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>95.7%</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>0.894</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44.3%</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
           <t>85.7%</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>95.7%</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>0.903</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>37.1%</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>75.7%</t>
-        </is>
-      </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>0.608</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>92.9%</t>
         </is>
       </c>
     </row>

--- a/SCIE용/산출물/엑셀/15_g1_g2_g3_g4_summary.xlsx
+++ b/SCIE용/산출물/엑셀/15_g1_g2_g3_g4_summary.xlsx
@@ -163,7 +163,7 @@
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
@@ -173,7 +173,7 @@
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -220,12 +220,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -235,7 +235,7 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -282,12 +282,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -297,37 +297,37 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>0.572</t>
         </is>
       </c>
       <c r="K4" s="0" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -344,7 +344,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -359,37 +359,37 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>0.903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>0.620</t>
         </is>
       </c>
       <c r="K5" s="0" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>87.1%</t>
         </is>
       </c>
     </row>
